--- a/appointments.xlsx
+++ b/appointments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,7 +434,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -577,10 +577,71 @@
           <t>booked</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>2026-03-26 12:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ayush</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8284884735</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>abhay</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dermatology</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>chest pain</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-03-29 13:49:58</t>
         </is>
       </c>
     </row>

--- a/appointments.xlsx
+++ b/appointments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -638,10 +638,132 @@
           <t>booked</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>2026-03-29 13:49:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ayush</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8284884735</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dr. Aisha Patel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>chest pain</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:06:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1234565432</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dr. Aisha Patel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>chest pain</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-04-27 21:12:05</t>
         </is>
       </c>
     </row>
